--- a/assets/Housing Study/Job Market/Telluride job market, print and employer boards.xlsx
+++ b/assets/Housing Study/Job Market/Telluride job market, print and employer boards.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and limits" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telski openings" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Town of Telluride openings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="County openings" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Every ad'!$A$4:$H$176</definedName>
@@ -122,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,6 +167,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8868,4 +8870,175 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>San Miguel County, all open positions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot from the county job board on August 2, 2026. Salary appears only after the page runs its scripts, so each figure has to be read from the live page one at a time. Three have been read so far.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Position title</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Advertised pay range</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Housing mentioned</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Parks and Open Space Manager</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>$89,316 - $100,027</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Planning Director</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>$116,454 to $132,175</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Correctional Officer / Emergency Dispatcher - Telluride</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>not yet read</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Deputy Sheriff - Operations</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>not yet read</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Equipment Mechanic - Road and Bridge</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>not yet read</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Equipment Operator - Road &amp; Bridge</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>none listed</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Lead Worker - Road &amp; Bridge (Egnar)</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>not yet read</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Light Equipment Operator - Road &amp; Bridge</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>not yet read</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Senior Equipment Operator (Norwood)</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>not yet read</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/assets/Housing Study/Job Market/Telluride job market, print and employer boards.xlsx
+++ b/assets/Housing Study/Job Market/Telluride job market, print and employer boards.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,6 +83,11 @@
       <color rgb="008A97A5"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -123,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,6 +173,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1014,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1052,243 +1063,192 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>CAUTION: the per-edition figures and their total count ad APPEARANCES, not distinct jobs. 172 appearances = about 67 distinct ads, since an ad runs about 2.6 weeks. See Method and limits, Limit 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>BLS SOC major group</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>April 9-15, 2026</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>April 16-22, 2026</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>April 23-29, 2026</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>April 30-May 6, 2026</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>May 7-13, 2026</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>May 14-20, 2026</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>May 21-27, 2026</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>May 28-June 3, 2026</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>June 4-10, 2026</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>June 11-17, 2026</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>June 18-24, 2026</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>June 25-July 1, 2026</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>July 2-8, 2026</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>July 9-15, 2026</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>July 16-22, 2026</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>July 23-29, 2026</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>July 30-August 5, 2026</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="C6" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="R6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="6" t="n"/>
       <c r="S6" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>1</v>
@@ -1300,26 +1260,26 @@
         <v>2</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" s="6" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="Q7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="R7" s="6" t="n"/>
       <c r="S7" s="7" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -1335,194 +1295,214 @@
         <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="n">
+      <c r="M8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
+      <c r="N8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="S8" s="7" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="6" t="n">
         <v>2</v>
       </c>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
       <c r="L9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="N9" s="6" t="n"/>
       <c r="O9" s="6" t="n"/>
-      <c r="P9" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="P9" s="6" t="n"/>
       <c r="Q9" s="6" t="n"/>
       <c r="R9" s="6" t="n"/>
       <c r="S9" s="7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="I10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O10" s="6" t="n"/>
       <c r="P10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6" t="n"/>
       <c r="R10" s="6" t="n"/>
       <c r="S10" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="F11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="6" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" s="6" t="n"/>
       <c r="S11" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="6" t="n"/>
+      <c r="D12" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
       <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
+      <c r="K12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="O12" s="6" t="n"/>
       <c r="P12" s="6" t="n"/>
       <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="6" t="n"/>
+      <c r="R12" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="S12" s="7" t="n">
         <v>8</v>
       </c>
@@ -1530,41 +1510,37 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="C13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="6" t="n"/>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="H13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="I13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
       <c r="L13" s="6" t="n"/>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="O13" s="6" t="n"/>
       <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q13" s="6" t="n"/>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="7" t="n">
         <v>8</v>
@@ -1573,83 +1549,89 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
+          <t>33-0000 Protective Service</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="C14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="6" t="n"/>
-      <c r="R14" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="O14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="6" t="n"/>
       <c r="S14" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>43-0000 Office and Administrative Support</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="O15" s="6" t="n"/>
       <c r="P15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="n"/>
+      <c r="R15" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="S15" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Other or not stated</t>
+          <t>43-0000 Office and Administrative Support</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -1658,10 +1640,10 @@
       <c r="C16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="D16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
@@ -1671,39 +1653,39 @@
       <c r="L16" s="6" t="n"/>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
+      <c r="O16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="Q16" s="6" t="n"/>
-      <c r="R16" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R16" s="6" t="n"/>
       <c r="S16" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>15-0000 Computer and Mathematical</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="E17" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="6" t="n"/>
       <c r="M17" s="6" t="n"/>
@@ -1711,7 +1693,9 @@
       <c r="O17" s="6" t="n"/>
       <c r="P17" s="6" t="n"/>
       <c r="Q17" s="6" t="n"/>
-      <c r="R17" s="6" t="n"/>
+      <c r="R17" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="S17" s="7" t="n">
         <v>4</v>
       </c>
@@ -1719,7 +1703,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
+          <t>15-0000 Computer and Mathematical</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
@@ -1727,32 +1711,34 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="G18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
       <c r="O18" s="6" t="n"/>
       <c r="P18" s="6" t="n"/>
       <c r="Q18" s="6" t="n"/>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>17-0000 Architecture and Engineering</t>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
@@ -1762,51 +1748,53 @@
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
+      <c r="K19" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="L19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M19" s="6" t="n"/>
+      <c r="M19" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N19" s="6" t="n"/>
       <c r="O19" s="6" t="n"/>
       <c r="P19" s="6" t="n"/>
       <c r="Q19" s="6" t="n"/>
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>47-0000 Construction and Extraction</t>
+          <t>17-0000 Architecture and Engineering</t>
         </is>
       </c>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
+      <c r="I20" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="L20" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
       <c r="O20" s="6" t="n"/>
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n"/>
-      <c r="R20" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R20" s="6" t="n"/>
       <c r="S20" s="7" t="n">
         <v>2</v>
       </c>
@@ -1814,30 +1802,30 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>13-0000 Business and Financial Operations</t>
+          <t>47-0000 Construction and Extraction</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
+      <c r="D21" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="I21" s="6" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
       <c r="O21" s="6" t="n"/>
       <c r="P21" s="6" t="n"/>
       <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="n"/>
+      <c r="R21" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="S21" s="7" t="n">
         <v>2</v>
       </c>
@@ -1845,7 +1833,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>19-0000 Life, Physical, and Social Science</t>
+          <t>13-0000 Business and Financial Operations</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
@@ -1855,26 +1843,28 @@
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
       <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
+      <c r="I22" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
       <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
+      <c r="M22" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="N22" s="6" t="n"/>
       <c r="O22" s="6" t="n"/>
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R22" s="6" t="n"/>
       <c r="S22" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>23-0000 Legal</t>
+          <t>19-0000 Life, Physical, and Social Science</t>
         </is>
       </c>
       <c r="B23" s="6" t="n"/>
@@ -1884,9 +1874,7 @@
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="6" t="n"/>
@@ -1895,244 +1883,275 @@
       <c r="O23" s="6" t="n"/>
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="n"/>
-      <c r="R23" s="6" t="n"/>
+      <c r="R23" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="S23" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>23-0000 Legal</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+      <c r="N24" s="6" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n"/>
+      <c r="Q24" s="6" t="n"/>
+      <c r="R24" s="6" t="n"/>
+      <c r="S24" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>All help-wanted ads</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B25" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C25" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D25" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E25" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F25" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="J24" s="9" t="n">
+      <c r="J25" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="K24" s="9" t="n">
+      <c r="K25" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="L24" s="9" t="n">
+      <c r="L25" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M25" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="N24" s="9" t="n">
+      <c r="N25" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="O24" s="9" t="n">
+      <c r="O25" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="P24" s="9" t="n">
+      <c r="P25" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q25" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R25" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="S24" s="9" t="n">
+      <c r="S25" s="9" t="n">
         <v>172</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Ads stating a wage</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B26" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C26" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D26" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E26" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F26" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="G26" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="H25" s="11" t="n">
+      <c r="H26" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="I26" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J26" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="K25" s="11" t="n">
+      <c r="K26" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="L26" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="M25" s="11" t="n">
+      <c r="M26" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="N25" s="11" t="n">
+      <c r="N26" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="O25" s="11" t="n">
+      <c r="O26" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="P25" s="11" t="n">
+      <c r="P26" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="Q25" s="11" t="n">
+      <c r="Q26" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="11" t="n">
+      <c r="R26" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="S25" s="11" t="n">
+      <c r="S26" s="11" t="n">
         <v>84</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Ads saying pay DOE</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="9" t="n">
+      <c r="B27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D27" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F27" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="9" t="n">
+      <c r="H27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="I27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="9" t="n">
+      <c r="J27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K27" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L27" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="9" t="n">
+      <c r="N27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="O26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="9" t="n"/>
-      <c r="R26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" s="9" t="n">
+      <c r="O27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" s="9" t="n">
         <v>43</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Ads offering housing</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="11" t="n">
+      <c r="B28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="O27" s="11" t="n">
+      <c r="O28" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="P27" s="11" t="n">
+      <c r="P28" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" s="11" t="n"/>
-      <c r="S27" s="11" t="n">
+      <c r="Q28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" s="11" t="n"/>
+      <c r="S28" s="11" t="n">
         <v>17</v>
       </c>
     </row>
@@ -7215,7 +7234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7322,28 +7341,64 @@
     <row r="14">
       <c r="A14" s="17" t="inlineStr"/>
     </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+    <row r="15" ht="74" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Limit 4: repeat ads</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>The headline ad count is the number of ad APPEARANCES, not distinct jobs. Across the seventeen editions there are 172 appearances but only about 67 distinct advertisements, because an ad typically runs about 2.6 weeks. The longest ran eight straight weeks. Wage figures are unaffected: the median is $55,000 counting appearances and $54,080 counting distinct ads. The share offering housing IS affected, and heavily: 17 appearances collapse to 6 distinct ads from only 3 employers, so the count of appearances should never be read as employers competing on housing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="74" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Limit 5: postings are requisitions, not headcount</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>This applies to the three employer-board sheets, not the classifieds. A job board lists openings, and one opening can be one hire or dozens. Roughly 19 of Telski's seasonal postings are open-ended mass hires (ski instructors, lift operators, snowmakers, trail safety, retail sales, tavern front of house), while all 8 year-round postings and most seasonal supervisory postings are single positions. So the true headcount sought is far larger than 36, and because the mass-hire postings are almost entirely seasonal, weighting by people would push the seasonal share well ABOVE the 72 percent shown here rather than below it. Never read the posting count as a count of workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="74" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Winter hiring, partly covered</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Limit 3 notes that the classifieds cover April through early August only. The employer-board sheets partly fill that gap, because they were captured on August 2 and already advertise winter roles, including a lift operator explicitly labelled Winter and an Allred's winter sous chef. So the boards give a summer snapshot of winter hiring, even though the classifieds do not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Why this beats the website</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>The classifieds page on the newspaper website shows only promoted ads and strips out all pay figures. The printed section carries the complete listing and the wages, which is why the print editions are the better source.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Compiled by</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Livable Telluride, from e-edition PDFs.</t>
         </is>
@@ -7360,7 +7415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7384,112 +7439,111 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Open positions</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="n">
-        <v>36</v>
-      </c>
-    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>CAUTION: these are POSTINGS, not people. One posting (ski instructor, lift operator, snowmaker, server) can be many hires. Headcount sought is far higher than 36, and more seasonal than 72%. See Method and limits, Limit 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Open positions</t>
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
           <t>Year round</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B7" s="19" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>BLS SOC major group</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Open positions</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>39-0000 Personal Care and Service</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Other or not stated</t>
+          <t>35-0000 Food Preparation and Serving Related</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
+          <t>Other or not stated</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>43-0000 Office and Administrative Support</t>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>43-0000 Office and Administrative Support</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
@@ -7499,7 +7553,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>15-0000 Computer and Mathematical</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -7509,7 +7563,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
+          <t>15-0000 Computer and Mathematical</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -7519,103 +7573,87 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>53-0000 Transportation and Material Moving</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B19" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Position title</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Division</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Employment type</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>BLS SOC major group</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Administrative Coordinator</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Reception</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Year Round</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>43-0000 Office and Administrative Support</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Allred's AM Winter Sous Chef</t>
+          <t>Administrative Coordinator</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Allred's Restaurant</t>
+          <t>Reception</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Food and Beverage</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Year Round</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>43-0000 Office and Administrative Support</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Bon Vivant Operations Manager</t>
+          <t>Allred's AM Winter Sous Chef</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Bon Vivant</t>
+          <t>Allred's Restaurant</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -7630,24 +7668,24 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>35-0000 Food Preparation and Serving Related</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Children's Group Ski Instructor</t>
+          <t>Bon Vivant Operations Manager</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Children's Instruction</t>
+          <t>Bon Vivant</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Ski School</t>
+          <t>Food and Beverage</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -7657,26 +7695,26 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Children's Ski &amp; Snowboard School, Rental Technician Supervisor</t>
+          <t>Children's Group Ski Instructor</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
+          <t>Children's Instruction</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
           <t>Ski School</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Ski School</t>
-        </is>
-      </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Seasonal</t>
@@ -7684,14 +7722,14 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Children's Ski &amp; Snowboard School, Indoor Attendant</t>
+          <t>Children's Ski &amp; Snowboard School, Rental Technician Supervisor</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -7706,46 +7744,46 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Clubhouse Bartender</t>
+          <t>Children's Ski &amp; Snowboard School, Indoor Attendant</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Clubhouse</t>
+          <t>Ski School</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Golf and Members' Club</t>
+          <t>Ski School</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Clubhouse Cook</t>
+          <t>Clubhouse Bartender</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -7772,17 +7810,17 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Fully Certified Ski Lesson Instructor</t>
+          <t>Clubhouse Cook</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Ski School</t>
+          <t>Clubhouse</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Ski School</t>
+          <t>Golf and Members' Club</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -7792,78 +7830,78 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Other or not stated</t>
+          <t>35-0000 Food Preparation and Serving Related</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Inn at Lost Creek Front Office Manager</t>
+          <t>Fully Certified Ski Lesson Instructor</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Inn at Lost Creek</t>
+          <t>Ski School</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Inn at Lost Creek</t>
+          <t>Ski School</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Year Round</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>Other or not stated</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Lift Operator I (Winter)</t>
+          <t>Inn at Lost Creek Front Office Manager</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Lift Operations</t>
+          <t>Inn at Lost Creek</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Mountain Operations</t>
+          <t>Inn at Lost Creek</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Year Round</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Outside Services Attendant</t>
+          <t>Lift Operator I (Winter)</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Outside Services</t>
+          <t>Lift Operations</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Golf and Members' Club</t>
+          <t>Mountain Operations</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -7880,17 +7918,17 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Peaks Resort &amp; Spa Cosmetologist</t>
+          <t>Outside Services Attendant</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Peaks Spa</t>
+          <t>Outside Services</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Spa at The Peaks Resort</t>
+          <t>Golf and Members' Club</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -7907,7 +7945,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Peaks Resort &amp; Spa Massage Therapist</t>
+          <t>Peaks Resort &amp; Spa Cosmetologist</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -7934,17 +7972,17 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Private Lessons Supervisor</t>
+          <t>Peaks Resort &amp; Spa Massage Therapist</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Ski School</t>
+          <t>Peaks Spa</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Ski School</t>
+          <t>Spa at The Peaks Resort</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -7954,24 +7992,24 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Retail Sales Associate - Sunshine / Guest Service Store</t>
+          <t>Private Lessons Supervisor</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Ski School</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Ski School</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -7981,14 +8019,14 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Retail Warehouse Associate/Driver</t>
+          <t>Retail Sales Associate - Sunshine / Guest Service Store</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -8008,132 +8046,132 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Senior Systems Administrator</t>
+          <t>Retail Warehouse Associate/Driver</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Information Systems</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Year Round</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>15-0000 Computer and Mathematical</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Ski Cub Instructor</t>
+          <t>Senior Systems Administrator</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Nursery</t>
+          <t>Information Systems</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Ski School</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Not stated</t>
+          <t>Year Round</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Other or not stated</t>
+          <t>15-0000 Computer and Mathematical</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Ski Patrol Manager - Training</t>
+          <t>Ski Cub Instructor</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Ski Patrol</t>
+          <t>Nursery</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Mountain Operations</t>
+          <t>Ski School</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Year Round</t>
+          <t>Not stated</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
+          <t>Other or not stated</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Ski Valet Attendant</t>
+          <t>Ski Patrol Manager - Training</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Slopeside Lockers</t>
+          <t>Ski Patrol</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Resort Services</t>
+          <t>Mountain Operations</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Year Round</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>33-0000 Protective Service</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Snowmaker</t>
+          <t>Ski Valet Attendant</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Snowmaking</t>
+          <t>Slopeside Lockers</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Mountain Operations</t>
+          <t>Resort Services</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -8143,14 +8181,14 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Snowmaking Foreman</t>
+          <t>Snowmaker</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -8170,14 +8208,14 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Snowmaking Technician</t>
+          <t>Snowmaking Foreman</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -8197,68 +8235,68 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Spa Concierge</t>
+          <t>Snowmaking Technician</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Peaks Spa</t>
+          <t>Snowmaking</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Spa at The Peaks Resort</t>
+          <t>Mountain Operations</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Year Round</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Telluride Sports Cimarron Store Manager</t>
+          <t>Spa Concierge</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Peaks Spa</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Spa at The Peaks Resort</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Year Round</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Telluride Sports Gondola Plaza Store Manager</t>
+          <t>Telluride Sports Cimarron Store Manager</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -8273,7 +8311,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Year Round</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -8285,7 +8323,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Telluride Sports Peaks Store Manager</t>
+          <t>Telluride Sports Gondola Plaza Store Manager</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -8300,7 +8338,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Seasonal</t>
+          <t>Year Round</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -8312,17 +8350,17 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Tomboy Tavern Backwaiter</t>
+          <t>Telluride Sports Peaks Store Manager</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Tomboy Tavern</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Food and Beverage</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -8332,14 +8370,14 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Other or not stated</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Tomboy Tavern Bartender</t>
+          <t>Tomboy Tavern Backwaiter</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
@@ -8359,14 +8397,14 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>Other or not stated</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Tomboy Tavern Host</t>
+          <t>Tomboy Tavern Bartender</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -8393,7 +8431,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Tomboy Tavern Server</t>
+          <t>Tomboy Tavern Host</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -8420,17 +8458,17 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Trail Safety Team Member</t>
+          <t>Tomboy Tavern Server</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Trail Safety</t>
+          <t>Tomboy Tavern</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Mountain Operations</t>
+          <t>Food and Beverage</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -8440,19 +8478,19 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Other or not stated</t>
+          <t>35-0000 Food Preparation and Serving Related</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Vehicle Mechanic II</t>
+          <t>Trail Safety Team Member</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Vehicle Maintenance</t>
+          <t>Trail Safety</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -8462,29 +8500,29 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Year Round</t>
+          <t>Seasonal</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
+          <t>Other or not stated</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Warehouse &amp; Delivery Attendant</t>
+          <t>Vehicle Mechanic II</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>F &amp; B Admin</t>
+          <t>Vehicle Maintenance</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Food and Beverage</t>
+          <t>Mountain Operations</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -8494,32 +8532,59 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
+          <t>Warehouse &amp; Delivery Attendant</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>F &amp; B Admin</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Food and Beverage</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Year Round</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
           <t>Zipline Driver / First Responder</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Zipline Adventures</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Zipline Adventures</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Seasonal</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>53-0000 Transportation and Material Moving</t>
         </is>
@@ -8536,7 +8601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -8559,54 +8624,40 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>CAUTION: these are POSTINGS, not people. See Method and limits, Limit 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Position title</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Employment type</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Advertised pay range</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>BLS SOC major group</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Administrative Assistant</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>not yet collected</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>43-0000 Office and Administrative Support</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Deputy Marshal (Police Officer)</t>
+          <t>Administrative Assistant</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -8621,14 +8672,14 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
+          <t>43-0000 Office and Administrative Support</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>Deputy Marshal (Police Officer)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -8643,14 +8694,14 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>33-0000 Protective Service</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Human Resources Director</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -8665,14 +8716,14 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>13-0000 Business and Financial Operations</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Senior Accountant</t>
+          <t>Human Resources Director</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -8694,7 +8745,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Senior Planner</t>
+          <t>Senior Accountant</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -8709,14 +8760,14 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>19-0000 Life, Physical, and Social Science</t>
+          <t>13-0000 Business and Financial Operations</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Water Wastewater Driver and Operator D</t>
+          <t>Senior Planner</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -8731,14 +8782,14 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
+          <t>19-0000 Life, Physical, and Social Science</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Water Wastewater Lab Tech/Operator D</t>
+          <t>Water Wastewater Driver and Operator D</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -8753,14 +8804,14 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Other or not stated</t>
+          <t>53-0000 Transportation and Material Moving</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Pretreatment Program Manager</t>
+          <t>Water Wastewater Lab Tech/Operator D</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -8775,14 +8826,14 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>Other or not stated</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Town Facilities Maintenance Technician II</t>
+          <t>Pretreatment Program Manager</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -8797,14 +8848,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Street Maintenance Technician I</t>
+          <t>Town Facilities Maintenance Technician II</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -8812,9 +8863,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>$47,439 - $64,043 per year</t>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>not yet collected</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -8826,7 +8877,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Street Maintenance Technician II</t>
+          <t>Street Maintenance Technician I</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -8834,9 +8885,9 @@
           <t>Full Time</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>not yet collected</t>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>$47,439 - $64,043 per year</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -8848,20 +8899,42 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>Street Maintenance Technician II</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>not yet collected</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>Water Wastewater Driver and Operator C</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>not yet collected</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>53-0000 Transportation and Material Moving</t>
         </is>
@@ -8878,7 +8951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -8900,70 +8973,65 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>CAUTION: these are POSTINGS, not people. See Method and limits, Limit 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Position title</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Advertised pay range</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Housing mentioned</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Parks and Open Space Manager</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>$89,316 - $100,027</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Planning Director</t>
+          <t>Parks and Open Space Manager</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>$116,454 to $132,175</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>$89,316 - $100,027</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Correctional Officer / Emergency Dispatcher - Telluride</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>not yet read</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
+          <t>Planning Director</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>$116,454 to $132,175</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Deputy Sheriff - Operations</t>
+          <t>Correctional Officer / Emergency Dispatcher - Telluride</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
@@ -8976,7 +9044,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Heavy Equipment Mechanic - Road and Bridge</t>
+          <t>Deputy Sheriff - Operations</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -8989,12 +9057,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Heavy Equipment Operator - Road &amp; Bridge</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>none listed</t>
+          <t>Heavy Equipment Mechanic - Road and Bridge</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>not yet read</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
@@ -9002,12 +9070,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Lead Worker - Road &amp; Bridge (Egnar)</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>not yet read</t>
+          <t>Heavy Equipment Operator - Road &amp; Bridge</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>none listed</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr"/>
@@ -9015,7 +9083,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Light Equipment Operator - Road &amp; Bridge</t>
+          <t>Lead Worker - Road &amp; Bridge (Egnar)</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
@@ -9028,15 +9096,28 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>Light Equipment Operator - Road &amp; Bridge</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>not yet read</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>Senior Equipment Operator (Norwood)</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>not yet read</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr"/>
+      <c r="C14" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
